--- a/Ejercicio/EjercicioMapReduce.xlsx
+++ b/Ejercicio/EjercicioMapReduce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Downloads\Academia\AWS\aws_xideral\Ejercicio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54B6618A-CE70-4D53-9C5F-6946237D89F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B981784-ED47-444E-9232-9F2D557B6AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{1B25688D-8BD1-45C3-84D9-A7E9F7A51A20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>input</t>
   </si>
@@ -56,28 +56,40 @@
     <t>Reduce</t>
   </si>
   <si>
-    <t>[Hadoop,1]</t>
-  </si>
-  <si>
     <t>Hadoop es interesante</t>
   </si>
   <si>
-    <t>[es, 1]</t>
-  </si>
-  <si>
-    <t>[interesante,1]</t>
-  </si>
-  <si>
-    <t>[yo,1]</t>
-  </si>
-  <si>
-    <t>[aprendo.1]</t>
-  </si>
-  <si>
-    <t>[Hadoop,1,1]</t>
-  </si>
-  <si>
-    <t>[Hadoop,2]</t>
+    <t>(Hadoop,[1,1])</t>
+  </si>
+  <si>
+    <t>(Hadoop,1)</t>
+  </si>
+  <si>
+    <t>(es, 1)</t>
+  </si>
+  <si>
+    <t>(interesante,1)</t>
+  </si>
+  <si>
+    <t>(yo,1)</t>
+  </si>
+  <si>
+    <t>(aprendo.1)</t>
+  </si>
+  <si>
+    <t>(es, [1])</t>
+  </si>
+  <si>
+    <t>(aprendo,[1])</t>
+  </si>
+  <si>
+    <t>(interesante,[1])</t>
+  </si>
+  <si>
+    <t>(yo,[1])</t>
+  </si>
+  <si>
+    <t>(Hadoop,2)</t>
   </si>
 </sst>
 </file>
@@ -454,7 +466,7 @@
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -474,38 +486,38 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -513,29 +525,29 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
